--- a/dataset_agreed/saved_models/hyperparameter_optimized_runs/pointcloud_HPO_run_3/epoch_90/per_file_predictions_epoch_90.xlsx
+++ b/dataset_agreed/saved_models/hyperparameter_optimized_runs/pointcloud_HPO_run_3/epoch_90/per_file_predictions_epoch_90.xlsx
@@ -808,769 +808,769 @@
     <t>0,1,1,0</t>
   </si>
   <si>
-    <t>0.9842,0.0013,0.0014,0.0026</t>
-  </si>
-  <si>
-    <t>0.9103,0.0005,0.0009,0.1228</t>
-  </si>
-  <si>
-    <t>0.8840,0.0128,0.0189,0.0391</t>
-  </si>
-  <si>
-    <t>0.9624,0.0003,0.0005,0.0422</t>
-  </si>
-  <si>
-    <t>0.9378,0.0008,0.0014,0.0720</t>
-  </si>
-  <si>
-    <t>0.9386,0.0028,0.0022,0.0480</t>
-  </si>
-  <si>
-    <t>0.8846,0.0031,0.0053,0.0741</t>
-  </si>
-  <si>
-    <t>0.8904,0.0095,0.0018,0.0404</t>
-  </si>
-  <si>
-    <t>0.9783,0.0013,0.0006,0.0130</t>
-  </si>
-  <si>
-    <t>0.9173,0.0060,0.0035,0.0467</t>
-  </si>
-  <si>
-    <t>0.6204,0.0186,0.0284,0.3418</t>
-  </si>
-  <si>
-    <t>0.9781,0.0006,0.0002,0.0134</t>
-  </si>
-  <si>
-    <t>0.9772,0.0008,0.0212,0.0003</t>
-  </si>
-  <si>
-    <t>0.9530,0.0026,0.0553,0.0005</t>
-  </si>
-  <si>
-    <t>0.9871,0.0005,0.0124,0.0002</t>
-  </si>
-  <si>
-    <t>0.8660,0.0155,0.1021,0.0019</t>
-  </si>
-  <si>
-    <t>0.9818,0.0014,0.0088,0.0006</t>
-  </si>
-  <si>
-    <t>0.8093,0.1828,0.0168,0.0007</t>
-  </si>
-  <si>
-    <t>0.9765,0.0042,0.0078,0.0003</t>
-  </si>
-  <si>
-    <t>0.9086,0.0411,0.0164,0.0031</t>
-  </si>
-  <si>
-    <t>0.9673,0.0079,0.0076,0.0013</t>
-  </si>
-  <si>
-    <t>0.7817,0.1434,0.0469,0.0014</t>
-  </si>
-  <si>
-    <t>0.9267,0.0016,0.0290,0.0061</t>
-  </si>
-  <si>
-    <t>0.9849,0.0010,0.0067,0.0005</t>
-  </si>
-  <si>
-    <t>0.7212,0.0019,0.4341,0.0012</t>
-  </si>
-  <si>
-    <t>0.7693,0.0034,0.2075,0.0113</t>
-  </si>
-  <si>
-    <t>0.6815,0.0128,0.5403,0.0011</t>
-  </si>
-  <si>
-    <t>0.7009,0.0051,0.5542,0.0007</t>
-  </si>
-  <si>
-    <t>0.0903,0.0062,0.9432,0.0012</t>
-  </si>
-  <si>
-    <t>0.9875,0.0015,0.0045,0.0002</t>
-  </si>
-  <si>
-    <t>0.8648,0.0659,0.0375,0.0121</t>
-  </si>
-  <si>
-    <t>0.0123,0.0159,0.9829,0.0118</t>
-  </si>
-  <si>
-    <t>0.9792,0.0071,0.0032,0.0009</t>
-  </si>
-  <si>
-    <t>0.9571,0.0067,0.0093,0.0024</t>
-  </si>
-  <si>
-    <t>0.6967,0.0122,0.1110,0.0873</t>
-  </si>
-  <si>
-    <t>0.9120,0.0129,0.0255,0.0108</t>
-  </si>
-  <si>
-    <t>0.9377,0.0126,0.0220,0.0080</t>
-  </si>
-  <si>
-    <t>0.1656,0.1892,0.7646,0.0156</t>
-  </si>
-  <si>
-    <t>0.1825,0.0016,0.9019,0.0008</t>
-  </si>
-  <si>
-    <t>0.9546,0.0007,0.0804,0.0002</t>
-  </si>
-  <si>
-    <t>0.3627,0.0091,0.7757,0.0020</t>
-  </si>
-  <si>
-    <t>0.5129,0.0475,0.5980,0.0027</t>
-  </si>
-  <si>
-    <t>0.2745,0.6090,0.0845,0.0007</t>
-  </si>
-  <si>
-    <t>0.9267,0.0032,0.1050,0.0004</t>
-  </si>
-  <si>
-    <t>0.8604,0.0691,0.0445,0.0035</t>
-  </si>
-  <si>
-    <t>0.9711,0.0024,0.0105,0.0008</t>
-  </si>
-  <si>
-    <t>0.9826,0.0087,0.0011,0.0002</t>
-  </si>
-  <si>
-    <t>0.6333,0.3615,0.0165,0.0007</t>
-  </si>
-  <si>
-    <t>0.0879,0.0318,0.9320,0.0022</t>
-  </si>
-  <si>
-    <t>0.7460,0.0061,0.4041,0.0004</t>
-  </si>
-  <si>
-    <t>0.8950,0.0057,0.1044,0.0045</t>
-  </si>
-  <si>
-    <t>0.3927,0.0105,0.8237,0.0019</t>
-  </si>
-  <si>
-    <t>0.0784,0.0790,0.9402,0.0013</t>
-  </si>
-  <si>
-    <t>0.5134,0.0184,0.6825,0.0012</t>
-  </si>
-  <si>
-    <t>0.7169,0.0984,0.0038,0.0115</t>
-  </si>
-  <si>
-    <t>0.8436,0.0077,0.0056,0.1122</t>
-  </si>
-  <si>
-    <t>0.9141,0.0160,0.0035,0.0150</t>
-  </si>
-  <si>
-    <t>0.7950,0.0518,0.1386,0.0201</t>
-  </si>
-  <si>
-    <t>0.9759,0.0005,0.0010,0.0133</t>
-  </si>
-  <si>
-    <t>0.9385,0.0032,0.0026,0.0468</t>
-  </si>
-  <si>
-    <t>0.9542,0.0017,0.0006,0.0316</t>
-  </si>
-  <si>
-    <t>0.0232,0.6315,0.9484,0.0017</t>
-  </si>
-  <si>
-    <t>0.6417,0.0043,0.6444,0.0002</t>
-  </si>
-  <si>
-    <t>0.0863,0.0054,0.9400,0.0006</t>
-  </si>
-  <si>
-    <t>0.0996,0.4148,0.8004,0.0009</t>
-  </si>
-  <si>
-    <t>0.0229,0.0073,0.9873,0.0002</t>
-  </si>
-  <si>
-    <t>0.8616,0.1964,0.0020,0.0002</t>
-  </si>
-  <si>
-    <t>0.1349,0.9349,0.0093,0.0002</t>
-  </si>
-  <si>
-    <t>0.7390,0.0029,0.1858,0.0128</t>
-  </si>
-  <si>
-    <t>0.9781,0.0013,0.0112,0.0009</t>
-  </si>
-  <si>
-    <t>0.0390,0.5324,0.7455,0.0070</t>
-  </si>
-  <si>
-    <t>0.1476,0.1608,0.8416,0.0003</t>
-  </si>
-  <si>
-    <t>0.2442,0.2277,0.7354,0.0015</t>
-  </si>
-  <si>
-    <t>0.0193,0.9838,0.0549,0.0003</t>
-  </si>
-  <si>
-    <t>0.0430,0.3003,0.9215,0.0010</t>
-  </si>
-  <si>
-    <t>0.8233,0.0001,0.0020,0.1477</t>
-  </si>
-  <si>
-    <t>0.8233,0.0002,0.0005,0.3388</t>
-  </si>
-  <si>
-    <t>0.5587,0.0014,0.0006,0.6709</t>
-  </si>
-  <si>
-    <t>0.8858,0.0002,0.0007,0.1506</t>
-  </si>
-  <si>
-    <t>0.9115,0.0001,0.0026,0.0542</t>
-  </si>
-  <si>
-    <t>0.7936,0.0014,0.0086,0.1799</t>
-  </si>
-  <si>
-    <t>0.1251,0.3267,0.8675,0.0012</t>
-  </si>
-  <si>
-    <t>0.0349,0.0274,0.9884,0.0001</t>
-  </si>
-  <si>
-    <t>0.3942,0.0172,0.7974,0.0008</t>
-  </si>
-  <si>
-    <t>0.1224,0.0253,0.9082,0.0015</t>
-  </si>
-  <si>
-    <t>0.0555,0.5499,0.7856,0.0007</t>
-  </si>
-  <si>
-    <t>0.1606,0.0202,0.9502,0.0002</t>
-  </si>
-  <si>
-    <t>0.9179,0.0039,0.0018,0.0373</t>
-  </si>
-  <si>
-    <t>0.9507,0.0035,0.0006,0.0182</t>
-  </si>
-  <si>
-    <t>0.9196,0.0099,0.0047,0.0214</t>
-  </si>
-  <si>
-    <t>0.9771,0.0018,0.0007,0.0109</t>
-  </si>
-  <si>
-    <t>0.9199,0.0101,0.0059,0.0179</t>
-  </si>
-  <si>
-    <t>0.9696,0.0009,0.0006,0.0232</t>
-  </si>
-  <si>
-    <t>0.9339,0.0030,0.0008,0.0314</t>
-  </si>
-  <si>
-    <t>0.8966,0.0600,0.0139,0.0048</t>
-  </si>
-  <si>
-    <t>0.8770,0.0069,0.0023,0.0627</t>
-  </si>
-  <si>
-    <t>0.9510,0.0012,0.0005,0.0515</t>
-  </si>
-  <si>
-    <t>0.9447,0.0022,0.0039,0.0459</t>
-  </si>
-  <si>
-    <t>0.9527,0.0027,0.0018,0.0357</t>
-  </si>
-  <si>
-    <t>0.9081,0.0018,0.0004,0.0702</t>
-  </si>
-  <si>
-    <t>0.8448,0.0388,0.0272,0.0314</t>
-  </si>
-  <si>
-    <t>0.9810,0.0005,0.0005,0.0172</t>
-  </si>
-  <si>
-    <t>0.9353,0.0009,0.0004,0.0777</t>
-  </si>
-  <si>
-    <t>0.0272,0.0052,0.9883,0.0013</t>
-  </si>
-  <si>
-    <t>0.8508,0.0041,0.2712,0.0010</t>
-  </si>
-  <si>
-    <t>0.9881,0.0003,0.0091,0.0002</t>
-  </si>
-  <si>
-    <t>0.9761,0.0015,0.0151,0.0007</t>
-  </si>
-  <si>
-    <t>0.8068,0.0898,0.0239,0.0092</t>
-  </si>
-  <si>
-    <t>0.8331,0.0805,0.0174,0.0069</t>
-  </si>
-  <si>
-    <t>0.8987,0.0299,0.0158,0.0079</t>
-  </si>
-  <si>
-    <t>0.9182,0.0196,0.0089,0.0087</t>
-  </si>
-  <si>
-    <t>0.8067,0.1771,0.0137,0.0042</t>
-  </si>
-  <si>
-    <t>0.0473,0.9104,0.1229,0.0039</t>
-  </si>
-  <si>
-    <t>0.8589,0.0711,0.0337,0.0059</t>
-  </si>
-  <si>
-    <t>0.9359,0.0040,0.0231,0.0078</t>
-  </si>
-  <si>
-    <t>0.9775,0.0003,0.0139,0.0006</t>
-  </si>
-  <si>
-    <t>0.9921,0.0005,0.0026,0.0003</t>
-  </si>
-  <si>
-    <t>0.9809,0.0020,0.0072,0.0015</t>
-  </si>
-  <si>
-    <t>0.8346,0.0175,0.0835,0.0230</t>
-  </si>
-  <si>
-    <t>0.9847,0.0066,0.0013,0.0001</t>
-  </si>
-  <si>
-    <t>0.9425,0.0398,0.0040,0.0005</t>
-  </si>
-  <si>
-    <t>0.7576,0.1037,0.1004,0.0040</t>
-  </si>
-  <si>
-    <t>0.2018,0.7029,0.1861,0.0012</t>
-  </si>
-  <si>
-    <t>0.9669,0.0023,0.0101,0.0037</t>
-  </si>
-  <si>
-    <t>0.7627,0.1456,0.0326,0.0059</t>
-  </si>
-  <si>
-    <t>0.9413,0.0110,0.0278,0.0030</t>
-  </si>
-  <si>
-    <t>0.9763,0.0040,0.0038,0.0046</t>
-  </si>
-  <si>
-    <t>0.9791,0.0031,0.0013,0.0051</t>
-  </si>
-  <si>
-    <t>0.9406,0.0148,0.0028,0.0055</t>
-  </si>
-  <si>
-    <t>0.9315,0.0083,0.0071,0.0116</t>
-  </si>
-  <si>
-    <t>0.9264,0.0016,0.0033,0.0439</t>
-  </si>
-  <si>
-    <t>0.9601,0.0021,0.0053,0.0101</t>
-  </si>
-  <si>
-    <t>0.9481,0.0043,0.0028,0.0182</t>
-  </si>
-  <si>
-    <t>0.8921,0.0107,0.0085,0.0500</t>
-  </si>
-  <si>
-    <t>0.5220,0.0202,0.7151,0.0009</t>
-  </si>
-  <si>
-    <t>0.8343,0.0165,0.2454,0.0007</t>
-  </si>
-  <si>
-    <t>0.8890,0.0015,0.1734,0.0004</t>
-  </si>
-  <si>
-    <t>0.6986,0.0130,0.4875,0.0011</t>
-  </si>
-  <si>
-    <t>0.9304,0.0060,0.0521,0.0032</t>
-  </si>
-  <si>
-    <t>0.9669,0.0040,0.0122,0.0016</t>
-  </si>
-  <si>
-    <t>0.9124,0.0020,0.0878,0.0025</t>
-  </si>
-  <si>
-    <t>0.6574,0.0026,0.2419,0.0150</t>
-  </si>
-  <si>
-    <t>0.8044,0.0011,0.0035,0.3049</t>
-  </si>
-  <si>
-    <t>0.2381,0.0003,0.0121,0.7714</t>
-  </si>
-  <si>
-    <t>0.9017,0.0001,0.0015,0.0670</t>
-  </si>
-  <si>
-    <t>0.9482,0.0002,0.0007,0.0539</t>
-  </si>
-  <si>
-    <t>0.0516,0.7290,0.5705,0.0009</t>
-  </si>
-  <si>
-    <t>0.9738,0.0020,0.0007,0.0075</t>
-  </si>
-  <si>
-    <t>0.9049,0.0067,0.0318,0.0215</t>
-  </si>
-  <si>
-    <t>0.8468,0.0038,0.0051,0.1712</t>
-  </si>
-  <si>
-    <t>0.9247,0.0031,0.0018,0.0400</t>
-  </si>
-  <si>
-    <t>0.9384,0.0124,0.0075,0.0121</t>
-  </si>
-  <si>
-    <t>0.9701,0.0018,0.0016,0.0147</t>
-  </si>
-  <si>
-    <t>0.9824,0.0013,0.0006,0.0078</t>
-  </si>
-  <si>
-    <t>0.2420,0.1831,0.8300,0.0285</t>
-  </si>
-  <si>
-    <t>0.8353,0.0009,0.0033,0.1648</t>
-  </si>
-  <si>
-    <t>0.9685,0.0019,0.0017,0.0182</t>
-  </si>
-  <si>
-    <t>0.9084,0.0309,0.0094,0.0070</t>
-  </si>
-  <si>
-    <t>0.9813,0.0005,0.0029,0.0044</t>
-  </si>
-  <si>
-    <t>0.9894,0.0012,0.0028,0.0004</t>
-  </si>
-  <si>
-    <t>0.9443,0.0145,0.0172,0.0029</t>
-  </si>
-  <si>
-    <t>0.9820,0.0011,0.0019,0.0027</t>
-  </si>
-  <si>
-    <t>0.9753,0.0012,0.0037,0.0026</t>
-  </si>
-  <si>
-    <t>0.8819,0.0035,0.0029,0.1006</t>
-  </si>
-  <si>
-    <t>0.8951,0.0084,0.0025,0.0565</t>
-  </si>
-  <si>
-    <t>0.9792,0.0015,0.0006,0.0079</t>
-  </si>
-  <si>
-    <t>0.9546,0.0008,0.0023,0.0316</t>
-  </si>
-  <si>
-    <t>0.9576,0.0049,0.0023,0.0123</t>
-  </si>
-  <si>
-    <t>0.9045,0.0118,0.0162,0.0299</t>
-  </si>
-  <si>
-    <t>0.9523,0.0015,0.0015,0.0464</t>
-  </si>
-  <si>
-    <t>0.8841,0.0059,0.0137,0.0536</t>
-  </si>
-  <si>
-    <t>0.9418,0.0086,0.0060,0.0110</t>
-  </si>
-  <si>
-    <t>0.9312,0.0115,0.0135,0.0039</t>
-  </si>
-  <si>
-    <t>0.8852,0.0297,0.0148,0.0115</t>
-  </si>
-  <si>
-    <t>0.9682,0.0030,0.0020,0.0144</t>
-  </si>
-  <si>
-    <t>0.9669,0.0044,0.0021,0.0060</t>
-  </si>
-  <si>
-    <t>0.9628,0.0051,0.0049,0.0071</t>
-  </si>
-  <si>
-    <t>0.9696,0.0020,0.0013,0.0153</t>
-  </si>
-  <si>
-    <t>0.9408,0.0083,0.0018,0.0124</t>
-  </si>
-  <si>
-    <t>0.0014,0.1795,0.9970,0.0006</t>
-  </si>
-  <si>
-    <t>0.9291,0.0032,0.0022,0.0413</t>
-  </si>
-  <si>
-    <t>0.0822,0.0055,0.9685,0.0003</t>
-  </si>
-  <si>
-    <t>0.0585,0.0308,0.9770,0.0009</t>
-  </si>
-  <si>
-    <t>0.9551,0.0014,0.0607,0.0006</t>
-  </si>
-  <si>
-    <t>0.7020,0.0051,0.5177,0.0003</t>
-  </si>
-  <si>
-    <t>0.7604,0.0033,0.4047,0.0008</t>
-  </si>
-  <si>
-    <t>0.1262,0.0075,0.9247,0.0017</t>
-  </si>
-  <si>
-    <t>0.9076,0.0009,0.1335,0.0005</t>
-  </si>
-  <si>
-    <t>0.9459,0.0040,0.0390,0.0017</t>
-  </si>
-  <si>
-    <t>0.9759,0.0014,0.0114,0.0004</t>
-  </si>
-  <si>
-    <t>0.9349,0.0037,0.0619,0.0024</t>
-  </si>
-  <si>
-    <t>0.8482,0.0035,0.2523,0.0013</t>
-  </si>
-  <si>
-    <t>0.9747,0.0015,0.0168,0.0006</t>
-  </si>
-  <si>
-    <t>0.9283,0.0027,0.0568,0.0022</t>
-  </si>
-  <si>
-    <t>0.9815,0.0016,0.0064,0.0009</t>
-  </si>
-  <si>
-    <t>0.8162,0.0242,0.1905,0.0060</t>
-  </si>
-  <si>
-    <t>0.7779,0.1962,0.0021,0.0010</t>
-  </si>
-  <si>
-    <t>0.9608,0.0262,0.0052,0.0010</t>
-  </si>
-  <si>
-    <t>0.8946,0.0512,0.0114,0.0049</t>
-  </si>
-  <si>
-    <t>0.9760,0.0042,0.0008,0.0037</t>
-  </si>
-  <si>
-    <t>0.8836,0.0566,0.0021,0.0032</t>
-  </si>
-  <si>
-    <t>0.9643,0.0053,0.0071,0.0010</t>
-  </si>
-  <si>
-    <t>0.9193,0.0039,0.0302,0.0087</t>
-  </si>
-  <si>
-    <t>0.9930,0.0002,0.0027,0.0004</t>
-  </si>
-  <si>
-    <t>0.9892,0.0004,0.0066,0.0003</t>
-  </si>
-  <si>
-    <t>0.9537,0.0007,0.0243,0.0019</t>
-  </si>
-  <si>
-    <t>0.4767,0.0224,0.6938,0.0076</t>
-  </si>
-  <si>
-    <t>0.8032,0.0051,0.4028,0.0003</t>
-  </si>
-  <si>
-    <t>0.4477,0.0101,0.8157,0.0004</t>
-  </si>
-  <si>
-    <t>0.5351,0.0009,0.7705,0.0001</t>
-  </si>
-  <si>
-    <t>0.0314,0.1584,0.9559,0.0011</t>
-  </si>
-  <si>
-    <t>0.5730,0.0337,0.0066,0.1408</t>
-  </si>
-  <si>
-    <t>0.8227,0.0143,0.0349,0.0483</t>
-  </si>
-  <si>
-    <t>0.9339,0.0072,0.0021,0.0273</t>
-  </si>
-  <si>
-    <t>0.9422,0.0058,0.0019,0.0155</t>
-  </si>
-  <si>
-    <t>0.9564,0.0021,0.0007,0.0232</t>
-  </si>
-  <si>
-    <t>0.9585,0.0028,0.0013,0.0160</t>
-  </si>
-  <si>
-    <t>0.9462,0.0039,0.0004,0.0131</t>
-  </si>
-  <si>
-    <t>0.8359,0.0062,0.0018,0.0817</t>
-  </si>
-  <si>
-    <t>0.5337,0.0288,0.5396,0.0164</t>
-  </si>
-  <si>
-    <t>0.8190,0.0277,0.1356,0.0159</t>
-  </si>
-  <si>
-    <t>0.9668,0.0007,0.0053,0.0113</t>
-  </si>
-  <si>
-    <t>0.1668,0.0121,0.9328,0.0004</t>
-  </si>
-  <si>
-    <t>0.0511,0.0621,0.8859,0.0011</t>
-  </si>
-  <si>
-    <t>0.9129,0.0062,0.1215,0.0012</t>
-  </si>
-  <si>
-    <t>0.0390,0.0077,0.9843,0.0003</t>
-  </si>
-  <si>
-    <t>0.9404,0.0023,0.0683,0.0013</t>
-  </si>
-  <si>
-    <t>0.0091,0.0141,0.9935,0.0007</t>
-  </si>
-  <si>
-    <t>0.8702,0.0054,0.2182,0.0006</t>
-  </si>
-  <si>
-    <t>0.9587,0.0037,0.0115,0.0057</t>
-  </si>
-  <si>
-    <t>0.9896,0.0002,0.0059,0.0003</t>
-  </si>
-  <si>
-    <t>0.8706,0.0193,0.0813,0.0063</t>
-  </si>
-  <si>
-    <t>0.9673,0.0005,0.0208,0.0011</t>
-  </si>
-  <si>
-    <t>0.9290,0.0032,0.0014,0.0560</t>
-  </si>
-  <si>
-    <t>0.9858,0.0021,0.0006,0.0022</t>
-  </si>
-  <si>
-    <t>0.9359,0.0105,0.0025,0.0161</t>
-  </si>
-  <si>
-    <t>0.8678,0.0340,0.0066,0.0090</t>
-  </si>
-  <si>
-    <t>0.9886,0.0004,0.0001,0.0052</t>
-  </si>
-  <si>
-    <t>0.9025,0.0107,0.0048,0.0298</t>
-  </si>
-  <si>
-    <t>0.9771,0.0017,0.0005,0.0086</t>
-  </si>
-  <si>
-    <t>0.9922,0.0008,0.0002,0.0021</t>
-  </si>
-  <si>
-    <t>0.9070,0.0022,0.1317,0.0012</t>
-  </si>
-  <si>
-    <t>0.2110,0.0306,0.8639,0.0010</t>
-  </si>
-  <si>
-    <t>0.0071,0.0251,0.9951,0.0003</t>
-  </si>
-  <si>
-    <t>0.8843,0.0045,0.1421,0.0024</t>
-  </si>
-  <si>
-    <t>0.0381,0.0008,0.9763,0.0003</t>
-  </si>
-  <si>
-    <t>0.9709,0.0017,0.0096,0.0030</t>
-  </si>
-  <si>
-    <t>0.9467,0.0023,0.0646,0.0006</t>
-  </si>
-  <si>
-    <t>0.8152,0.0017,0.2195,0.0022</t>
-  </si>
-  <si>
-    <t>0.9853,0.0002,0.0003,0.0078</t>
-  </si>
-  <si>
-    <t>0.5663,0.0007,0.0147,0.3168</t>
-  </si>
-  <si>
-    <t>0.8442,0.0001,0.0040,0.0716</t>
-  </si>
-  <si>
-    <t>0.9058,0.0002,0.0011,0.1280</t>
-  </si>
-  <si>
-    <t>0.8555,0.0002,0.0003,0.3530</t>
-  </si>
-  <si>
-    <t>0.8116,0.0008,0.0138,0.0708</t>
+    <t>0.9017,0.0635,0.0029,0.0232</t>
+  </si>
+  <si>
+    <t>0.0347,0.0007,0.0001,0.9911</t>
+  </si>
+  <si>
+    <t>0.8842,0.0010,0.0001,0.2197</t>
+  </si>
+  <si>
+    <t>0.0255,0.0039,0.0007,0.9863</t>
+  </si>
+  <si>
+    <t>0.9990,0.0003,0.0000,0.0003</t>
+  </si>
+  <si>
+    <t>0.9970,0.0013,0.0000,0.0003</t>
+  </si>
+  <si>
+    <t>0.9969,0.0021,0.0002,0.0004</t>
+  </si>
+  <si>
+    <t>0.9979,0.0007,0.0001,0.0005</t>
+  </si>
+  <si>
+    <t>0.9957,0.0041,0.0002,0.0004</t>
+  </si>
+  <si>
+    <t>0.9965,0.0033,0.0002,0.0003</t>
+  </si>
+  <si>
+    <t>0.9980,0.0014,0.0004,0.0001</t>
+  </si>
+  <si>
+    <t>0.9984,0.0012,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.5428,0.0564,0.5291,0.0029</t>
+  </si>
+  <si>
+    <t>0.0106,0.0092,0.9801,0.0023</t>
+  </si>
+  <si>
+    <t>0.0233,0.0101,0.9848,0.0003</t>
+  </si>
+  <si>
+    <t>0.5377,0.0099,0.6031,0.0005</t>
+  </si>
+  <si>
+    <t>0.9215,0.0046,0.0805,0.0038</t>
+  </si>
+  <si>
+    <t>0.0024,0.9949,0.0016,0.0005</t>
+  </si>
+  <si>
+    <t>0.0004,0.9987,0.0008,0.0003</t>
+  </si>
+  <si>
+    <t>0.2471,0.8592,0.0047,0.0008</t>
+  </si>
+  <si>
+    <t>0.0025,0.9949,0.0015,0.0004</t>
+  </si>
+  <si>
+    <t>0.0001,0.9995,0.0002,0.0002</t>
+  </si>
+  <si>
+    <t>0.9114,0.0003,0.0502,0.0029</t>
+  </si>
+  <si>
+    <t>0.7136,0.0203,0.2255,0.0278</t>
+  </si>
+  <si>
+    <t>0.0010,0.0008,0.9979,0.0004</t>
+  </si>
+  <si>
+    <t>0.0538,0.0104,0.9232,0.0163</t>
+  </si>
+  <si>
+    <t>0.0448,0.0014,0.9748,0.0010</t>
+  </si>
+  <si>
+    <t>0.0149,0.0004,0.9897,0.0005</t>
+  </si>
+  <si>
+    <t>0.0037,0.0018,0.9942,0.0016</t>
+  </si>
+  <si>
+    <t>0.1683,0.8439,0.0238,0.0032</t>
+  </si>
+  <si>
+    <t>0.7640,0.2874,0.0148,0.0006</t>
+  </si>
+  <si>
+    <t>0.0028,0.0153,0.9960,0.0022</t>
+  </si>
+  <si>
+    <t>0.0086,0.9567,0.0227,0.0011</t>
+  </si>
+  <si>
+    <t>0.8047,0.1759,0.0666,0.0111</t>
+  </si>
+  <si>
+    <t>0.7376,0.2705,0.0199,0.0090</t>
+  </si>
+  <si>
+    <t>0.2464,0.8731,0.0010,0.0003</t>
+  </si>
+  <si>
+    <t>0.0035,0.9902,0.0390,0.0041</t>
+  </si>
+  <si>
+    <t>0.0167,0.8930,0.0654,0.0327</t>
+  </si>
+  <si>
+    <t>0.0088,0.0370,0.9850,0.0038</t>
+  </si>
+  <si>
+    <t>0.2643,0.0257,0.7474,0.0021</t>
+  </si>
+  <si>
+    <t>0.1417,0.0044,0.8029,0.0254</t>
+  </si>
+  <si>
+    <t>0.0105,0.1610,0.9599,0.0023</t>
+  </si>
+  <si>
+    <t>0.0057,0.9712,0.0177,0.0013</t>
+  </si>
+  <si>
+    <t>0.0086,0.0059,0.9794,0.0026</t>
+  </si>
+  <si>
+    <t>0.1017,0.1589,0.0118,0.8170</t>
+  </si>
+  <si>
+    <t>0.0015,0.9927,0.0104,0.0073</t>
+  </si>
+  <si>
+    <t>0.0023,0.9919,0.0102,0.0048</t>
+  </si>
+  <si>
+    <t>0.0037,0.9944,0.0070,0.0007</t>
+  </si>
+  <si>
+    <t>0.0067,0.1424,0.9173,0.0129</t>
+  </si>
+  <si>
+    <t>0.0023,0.0912,0.9929,0.0005</t>
+  </si>
+  <si>
+    <t>0.0189,0.0118,0.9608,0.0090</t>
+  </si>
+  <si>
+    <t>0.0045,0.0005,0.9947,0.0010</t>
+  </si>
+  <si>
+    <t>0.0313,0.0112,0.9659,0.0012</t>
+  </si>
+  <si>
+    <t>0.0020,0.3216,0.9849,0.0041</t>
+  </si>
+  <si>
+    <t>0.9947,0.0035,0.0004,0.0008</t>
+  </si>
+  <si>
+    <t>0.9900,0.0033,0.0037,0.0010</t>
+  </si>
+  <si>
+    <t>0.9937,0.0017,0.0037,0.0004</t>
+  </si>
+  <si>
+    <t>0.0092,0.0458,0.9787,0.0670</t>
+  </si>
+  <si>
+    <t>0.9946,0.0034,0.0011,0.0004</t>
+  </si>
+  <si>
+    <t>0.9834,0.0270,0.0007,0.0008</t>
+  </si>
+  <si>
+    <t>0.9763,0.0293,0.0025,0.0003</t>
+  </si>
+  <si>
+    <t>0.0087,0.8992,0.8255,0.0017</t>
+  </si>
+  <si>
+    <t>0.0166,0.0339,0.9763,0.0048</t>
+  </si>
+  <si>
+    <t>0.0108,0.0050,0.9813,0.0051</t>
+  </si>
+  <si>
+    <t>0.0006,0.9040,0.9940,0.0003</t>
+  </si>
+  <si>
+    <t>0.0041,0.0036,0.9894,0.0017</t>
+  </si>
+  <si>
+    <t>0.0021,0.9966,0.0028,0.0000</t>
+  </si>
+  <si>
+    <t>0.0075,0.9921,0.0007,0.0002</t>
+  </si>
+  <si>
+    <t>0.1748,0.0300,0.9038,0.0109</t>
+  </si>
+  <si>
+    <t>0.7014,0.0267,0.3796,0.0088</t>
+  </si>
+  <si>
+    <t>0.0019,0.0024,0.9964,0.0016</t>
+  </si>
+  <si>
+    <t>0.0002,0.9704,0.9953,0.0002</t>
+  </si>
+  <si>
+    <t>0.0012,0.9895,0.3419,0.0009</t>
+  </si>
+  <si>
+    <t>0.0004,0.9985,0.0026,0.0001</t>
+  </si>
+  <si>
+    <t>0.0013,0.9886,0.4367,0.0006</t>
+  </si>
+  <si>
+    <t>0.0573,0.0006,0.0101,0.9618</t>
+  </si>
+  <si>
+    <t>0.0007,0.0014,0.0001,0.9994</t>
+  </si>
+  <si>
+    <t>0.0006,0.0007,0.0000,0.9996</t>
+  </si>
+  <si>
+    <t>0.0028,0.0021,0.0003,0.9979</t>
+  </si>
+  <si>
+    <t>0.0189,0.0009,0.0005,0.9953</t>
+  </si>
+  <si>
+    <t>0.0078,0.0038,0.0014,0.9945</t>
+  </si>
+  <si>
+    <t>0.0002,0.9957,0.9654,0.0001</t>
+  </si>
+  <si>
+    <t>0.0014,0.6432,0.9935,0.0007</t>
+  </si>
+  <si>
+    <t>0.0156,0.5644,0.7214,0.0047</t>
+  </si>
+  <si>
+    <t>0.0084,0.5349,0.9636,0.0034</t>
+  </si>
+  <si>
+    <t>0.0014,0.9923,0.0939,0.0004</t>
+  </si>
+  <si>
+    <t>0.0060,0.9154,0.7281,0.0026</t>
+  </si>
+  <si>
+    <t>0.9965,0.0026,0.0003,0.0003</t>
+  </si>
+  <si>
+    <t>0.9958,0.0027,0.0008,0.0003</t>
+  </si>
+  <si>
+    <t>0.9982,0.0014,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.9947,0.0045,0.0006,0.0005</t>
+  </si>
+  <si>
+    <t>0.9986,0.0006,0.0000,0.0002</t>
+  </si>
+  <si>
+    <t>0.9990,0.0004,0.0000,0.0002</t>
+  </si>
+  <si>
+    <t>0.9895,0.0074,0.0015,0.0016</t>
+  </si>
+  <si>
+    <t>0.9951,0.0058,0.0004,0.0002</t>
+  </si>
+  <si>
+    <t>0.9992,0.0003,0.0000,0.0001</t>
+  </si>
+  <si>
+    <t>0.9978,0.0013,0.0000,0.0003</t>
+  </si>
+  <si>
+    <t>0.9993,0.0000,0.0000,0.0003</t>
+  </si>
+  <si>
+    <t>0.9987,0.0002,0.0000,0.0005</t>
+  </si>
+  <si>
+    <t>0.9990,0.0002,0.0000,0.0002</t>
+  </si>
+  <si>
+    <t>0.9891,0.0084,0.0028,0.0007</t>
+  </si>
+  <si>
+    <t>0.9985,0.0009,0.0002,0.0001</t>
+  </si>
+  <si>
+    <t>0.9990,0.0001,0.0000,0.0003</t>
+  </si>
+  <si>
+    <t>0.0276,0.0008,0.9874,0.0007</t>
+  </si>
+  <si>
+    <t>0.0208,0.0079,0.9781,0.0022</t>
+  </si>
+  <si>
+    <t>0.9037,0.0037,0.0417,0.0144</t>
+  </si>
+  <si>
+    <t>0.0017,0.0015,0.9951,0.0031</t>
+  </si>
+  <si>
+    <t>0.0071,0.9924,0.0004,0.0001</t>
+  </si>
+  <si>
+    <t>0.0008,0.9987,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.0197,0.9756,0.0028,0.0017</t>
+  </si>
+  <si>
+    <t>0.0037,0.9949,0.0005,0.0002</t>
+  </si>
+  <si>
+    <t>0.0014,0.9980,0.0002,0.0001</t>
+  </si>
+  <si>
+    <t>0.0015,0.9969,0.0003,0.0003</t>
+  </si>
+  <si>
+    <t>0.8623,0.1793,0.0064,0.0022</t>
+  </si>
+  <si>
+    <t>0.6629,0.0222,0.1726,0.1221</t>
+  </si>
+  <si>
+    <t>0.4844,0.0074,0.6502,0.0060</t>
+  </si>
+  <si>
+    <t>0.5862,0.0922,0.3323,0.0757</t>
+  </si>
+  <si>
+    <t>0.5372,0.2568,0.1395,0.0125</t>
+  </si>
+  <si>
+    <t>0.0847,0.0260,0.0578,0.8914</t>
+  </si>
+  <si>
+    <t>0.0003,0.9986,0.0049,0.0003</t>
+  </si>
+  <si>
+    <t>0.0048,0.9860,0.0027,0.0067</t>
+  </si>
+  <si>
+    <t>0.0023,0.9903,0.0042,0.0030</t>
+  </si>
+  <si>
+    <t>0.0003,0.9955,0.7711,0.0008</t>
+  </si>
+  <si>
+    <t>0.0045,0.9940,0.0006,0.0005</t>
+  </si>
+  <si>
+    <t>0.8628,0.1629,0.0083,0.0020</t>
+  </si>
+  <si>
+    <t>0.4386,0.6648,0.0039,0.0010</t>
+  </si>
+  <si>
+    <t>0.9956,0.0021,0.0006,0.0004</t>
+  </si>
+  <si>
+    <t>0.9961,0.0023,0.0006,0.0003</t>
+  </si>
+  <si>
+    <t>0.9945,0.0026,0.0013,0.0004</t>
+  </si>
+  <si>
+    <t>0.9868,0.0041,0.0038,0.0026</t>
+  </si>
+  <si>
+    <t>0.9978,0.0004,0.0003,0.0004</t>
+  </si>
+  <si>
+    <t>0.9908,0.0105,0.0006,0.0003</t>
+  </si>
+  <si>
+    <t>0.9979,0.0008,0.0001,0.0003</t>
+  </si>
+  <si>
+    <t>0.9944,0.0016,0.0018,0.0012</t>
+  </si>
+  <si>
+    <t>0.0017,0.9104,0.9802,0.0016</t>
+  </si>
+  <si>
+    <t>0.0095,0.7828,0.9153,0.0024</t>
+  </si>
+  <si>
+    <t>0.0077,0.0262,0.9720,0.0014</t>
+  </si>
+  <si>
+    <t>0.0138,0.1301,0.8985,0.0015</t>
+  </si>
+  <si>
+    <t>0.9741,0.0080,0.0103,0.0012</t>
+  </si>
+  <si>
+    <t>0.6094,0.0202,0.3560,0.0369</t>
+  </si>
+  <si>
+    <t>0.1608,0.0094,0.8951,0.0050</t>
+  </si>
+  <si>
+    <t>0.2754,0.0201,0.6974,0.0571</t>
+  </si>
+  <si>
+    <t>0.1062,0.0001,0.0007,0.9658</t>
+  </si>
+  <si>
+    <t>0.0004,0.0015,0.0010,0.9991</t>
+  </si>
+  <si>
+    <t>0.0026,0.0003,0.0001,0.9991</t>
+  </si>
+  <si>
+    <t>0.0094,0.0002,0.0005,0.9968</t>
+  </si>
+  <si>
+    <t>0.0005,0.9959,0.0387,0.0002</t>
+  </si>
+  <si>
+    <t>0.9986,0.0002,0.0002,0.0003</t>
+  </si>
+  <si>
+    <t>0.0578,0.9387,0.0018,0.0039</t>
+  </si>
+  <si>
+    <t>0.9951,0.0011,0.0005,0.0014</t>
+  </si>
+  <si>
+    <t>0.0184,0.9823,0.0013,0.0005</t>
+  </si>
+  <si>
+    <t>0.9948,0.0006,0.0013,0.0010</t>
+  </si>
+  <si>
+    <t>0.5136,0.0017,0.0006,0.7414</t>
+  </si>
+  <si>
+    <t>0.9912,0.0031,0.0018,0.0022</t>
+  </si>
+  <si>
+    <t>0.0087,0.1702,0.9534,0.0899</t>
+  </si>
+  <si>
+    <t>0.9387,0.0007,0.0003,0.1129</t>
+  </si>
+  <si>
+    <t>0.6747,0.0015,0.0006,0.5531</t>
+  </si>
+  <si>
+    <t>0.7090,0.3187,0.0100,0.0030</t>
+  </si>
+  <si>
+    <t>0.9827,0.0031,0.0059,0.0029</t>
+  </si>
+  <si>
+    <t>0.9793,0.0098,0.0059,0.0009</t>
+  </si>
+  <si>
+    <t>0.0805,0.8493,0.0795,0.0164</t>
+  </si>
+  <si>
+    <t>0.5369,0.3279,0.0762,0.0026</t>
+  </si>
+  <si>
+    <t>0.7931,0.1889,0.0343,0.0025</t>
+  </si>
+  <si>
+    <t>0.9928,0.0055,0.0012,0.0004</t>
+  </si>
+  <si>
+    <t>0.9988,0.0004,0.0002,0.0001</t>
+  </si>
+  <si>
+    <t>0.9953,0.0016,0.0003,0.0011</t>
+  </si>
+  <si>
+    <t>0.9964,0.0002,0.0001,0.0022</t>
+  </si>
+  <si>
+    <t>0.9940,0.0018,0.0004,0.0017</t>
+  </si>
+  <si>
+    <t>0.9920,0.0046,0.0025,0.0003</t>
+  </si>
+  <si>
+    <t>0.9937,0.0047,0.0007,0.0005</t>
+  </si>
+  <si>
+    <t>0.9933,0.0013,0.0011,0.0022</t>
+  </si>
+  <si>
+    <t>0.8927,0.1742,0.0006,0.0016</t>
+  </si>
+  <si>
+    <t>0.2872,0.8384,0.0007,0.0005</t>
+  </si>
+  <si>
+    <t>0.7991,0.2733,0.0024,0.0028</t>
+  </si>
+  <si>
+    <t>0.5750,0.1040,0.4845,0.0184</t>
+  </si>
+  <si>
+    <t>0.9959,0.0064,0.0001,0.0002</t>
+  </si>
+  <si>
+    <t>0.8441,0.1751,0.0130,0.0021</t>
+  </si>
+  <si>
+    <t>0.9949,0.0057,0.0005,0.0002</t>
+  </si>
+  <si>
+    <t>0.8899,0.1617,0.0004,0.0011</t>
+  </si>
+  <si>
+    <t>0.0026,0.0286,0.9968,0.0013</t>
+  </si>
+  <si>
+    <t>0.9920,0.0062,0.0012,0.0002</t>
+  </si>
+  <si>
+    <t>0.0015,0.0069,0.9967,0.0006</t>
+  </si>
+  <si>
+    <t>0.0008,0.0498,0.9973,0.0010</t>
+  </si>
+  <si>
+    <t>0.0364,0.0237,0.9598,0.0042</t>
+  </si>
+  <si>
+    <t>0.0036,0.0534,0.9937,0.0009</t>
+  </si>
+  <si>
+    <t>0.0013,0.0013,0.9978,0.0003</t>
+  </si>
+  <si>
+    <t>0.0018,0.0008,0.9970,0.0015</t>
+  </si>
+  <si>
+    <t>0.0031,0.0208,0.9786,0.0016</t>
+  </si>
+  <si>
+    <t>0.1156,0.0642,0.8554,0.0125</t>
+  </si>
+  <si>
+    <t>0.5632,0.0029,0.6326,0.0020</t>
+  </si>
+  <si>
+    <t>0.5274,0.0316,0.5347,0.0293</t>
+  </si>
+  <si>
+    <t>0.6180,0.1031,0.2772,0.0017</t>
+  </si>
+  <si>
+    <t>0.0986,0.1220,0.8707,0.0070</t>
+  </si>
+  <si>
+    <t>0.5069,0.3146,0.1936,0.0185</t>
+  </si>
+  <si>
+    <t>0.4282,0.0123,0.3087,0.1671</t>
+  </si>
+  <si>
+    <t>0.3114,0.0893,0.6556,0.0136</t>
+  </si>
+  <si>
+    <t>0.6663,0.4689,0.0076,0.0006</t>
+  </si>
+  <si>
+    <t>0.4821,0.6439,0.0071,0.0042</t>
+  </si>
+  <si>
+    <t>0.9905,0.0158,0.0002,0.0005</t>
+  </si>
+  <si>
+    <t>0.9924,0.0127,0.0002,0.0003</t>
+  </si>
+  <si>
+    <t>0.7747,0.4674,0.0002,0.0003</t>
+  </si>
+  <si>
+    <t>0.9009,0.0415,0.0477,0.0051</t>
+  </si>
+  <si>
+    <t>0.9106,0.0011,0.1094,0.0022</t>
+  </si>
+  <si>
+    <t>0.9054,0.0015,0.0147,0.0408</t>
+  </si>
+  <si>
+    <t>0.5659,0.0051,0.4747,0.0150</t>
+  </si>
+  <si>
+    <t>0.4326,0.0125,0.6305,0.0169</t>
+  </si>
+  <si>
+    <t>0.0094,0.0036,0.9803,0.0206</t>
+  </si>
+  <si>
+    <t>0.0615,0.1144,0.8870,0.0387</t>
+  </si>
+  <si>
+    <t>0.0047,0.0111,0.9869,0.0043</t>
+  </si>
+  <si>
+    <t>0.0762,0.0151,0.9034,0.0111</t>
+  </si>
+  <si>
+    <t>0.0037,0.0783,0.9345,0.0024</t>
+  </si>
+  <si>
+    <t>0.9975,0.0008,0.0001,0.0006</t>
+  </si>
+  <si>
+    <t>0.9891,0.0080,0.0013,0.0014</t>
+  </si>
+  <si>
+    <t>0.9919,0.0062,0.0019,0.0006</t>
+  </si>
+  <si>
+    <t>0.9753,0.0387,0.0018,0.0006</t>
+  </si>
+  <si>
+    <t>0.9944,0.0026,0.0001,0.0009</t>
+  </si>
+  <si>
+    <t>0.9971,0.0025,0.0002,0.0002</t>
+  </si>
+  <si>
+    <t>0.9948,0.0038,0.0005,0.0009</t>
+  </si>
+  <si>
+    <t>0.9968,0.0009,0.0001,0.0009</t>
+  </si>
+  <si>
+    <t>0.0363,0.0528,0.9598,0.0111</t>
+  </si>
+  <si>
+    <t>0.0159,0.1921,0.8843,0.0025</t>
+  </si>
+  <si>
+    <t>0.8806,0.0724,0.0508,0.0082</t>
+  </si>
+  <si>
+    <t>0.0057,0.0041,0.9889,0.0019</t>
+  </si>
+  <si>
+    <t>0.0064,0.0020,0.9848,0.0038</t>
+  </si>
+  <si>
+    <t>0.0328,0.0545,0.8561,0.0122</t>
+  </si>
+  <si>
+    <t>0.0041,0.0090,0.9949,0.0007</t>
+  </si>
+  <si>
+    <t>0.0119,0.0047,0.9759,0.0017</t>
+  </si>
+  <si>
+    <t>0.0028,0.0199,0.9905,0.0049</t>
+  </si>
+  <si>
+    <t>0.0106,0.0037,0.9818,0.0037</t>
+  </si>
+  <si>
+    <t>0.0291,0.0250,0.9421,0.0058</t>
+  </si>
+  <si>
+    <t>0.7920,0.0044,0.1779,0.0173</t>
+  </si>
+  <si>
+    <t>0.0693,0.0036,0.9369,0.0049</t>
+  </si>
+  <si>
+    <t>0.8660,0.0026,0.1384,0.0066</t>
+  </si>
+  <si>
+    <t>0.9891,0.0158,0.0007,0.0004</t>
+  </si>
+  <si>
+    <t>0.9959,0.0033,0.0004,0.0003</t>
+  </si>
+  <si>
+    <t>0.9954,0.0036,0.0007,0.0003</t>
+  </si>
+  <si>
+    <t>0.9964,0.0060,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.9988,0.0004,0.0001,0.0002</t>
+  </si>
+  <si>
+    <t>0.9941,0.0123,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.9888,0.0135,0.0015,0.0004</t>
+  </si>
+  <si>
+    <t>0.9957,0.0064,0.0000,0.0001</t>
+  </si>
+  <si>
+    <t>0.0636,0.0266,0.9455,0.0015</t>
+  </si>
+  <si>
+    <t>0.0036,0.0076,0.9872,0.0063</t>
+  </si>
+  <si>
+    <t>0.0111,0.0388,0.9722,0.0086</t>
+  </si>
+  <si>
+    <t>0.0264,0.0541,0.9360,0.0022</t>
+  </si>
+  <si>
+    <t>0.0060,0.0098,0.9869,0.0011</t>
+  </si>
+  <si>
+    <t>0.0056,0.0005,0.8457,0.3098</t>
+  </si>
+  <si>
+    <t>0.3192,0.0480,0.6601,0.0142</t>
+  </si>
+  <si>
+    <t>0.1260,0.0086,0.4131,0.1930</t>
+  </si>
+  <si>
+    <t>0.5717,0.0055,0.0004,0.5677</t>
+  </si>
+  <si>
+    <t>0.0304,0.0077,0.0014,0.9871</t>
+  </si>
+  <si>
+    <t>0.0664,0.0041,0.0014,0.9722</t>
+  </si>
+  <si>
+    <t>0.0031,0.0002,0.0004,0.9989</t>
+  </si>
+  <si>
+    <t>0.0017,0.0005,0.0005,0.9990</t>
+  </si>
+  <si>
+    <t>0.8363,0.0016,0.0099,0.1155</t>
   </si>
 </sst>
 </file>
@@ -1967,7 +1967,7 @@
         <v>260</v>
       </c>
       <c r="C3" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D3" t="s">
         <v>265</v>
@@ -1995,7 +1995,7 @@
         <v>260</v>
       </c>
       <c r="C5" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D5" t="s">
         <v>267</v>
@@ -2121,7 +2121,7 @@
         <v>259</v>
       </c>
       <c r="C14" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D14" t="s">
         <v>276</v>
@@ -2135,7 +2135,7 @@
         <v>261</v>
       </c>
       <c r="C15" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D15" t="s">
         <v>277</v>
@@ -2149,7 +2149,7 @@
         <v>261</v>
       </c>
       <c r="C16" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D16" t="s">
         <v>278</v>
@@ -2163,7 +2163,7 @@
         <v>261</v>
       </c>
       <c r="C17" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D17" t="s">
         <v>279</v>
@@ -2191,7 +2191,7 @@
         <v>262</v>
       </c>
       <c r="C19" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D19" t="s">
         <v>281</v>
@@ -2205,7 +2205,7 @@
         <v>262</v>
       </c>
       <c r="C20" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D20" t="s">
         <v>282</v>
@@ -2219,7 +2219,7 @@
         <v>262</v>
       </c>
       <c r="C21" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D21" t="s">
         <v>283</v>
@@ -2233,7 +2233,7 @@
         <v>262</v>
       </c>
       <c r="C22" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D22" t="s">
         <v>284</v>
@@ -2247,7 +2247,7 @@
         <v>262</v>
       </c>
       <c r="C23" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D23" t="s">
         <v>285</v>
@@ -2289,7 +2289,7 @@
         <v>261</v>
       </c>
       <c r="C26" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D26" t="s">
         <v>288</v>
@@ -2303,7 +2303,7 @@
         <v>261</v>
       </c>
       <c r="C27" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D27" t="s">
         <v>289</v>
@@ -2359,7 +2359,7 @@
         <v>259</v>
       </c>
       <c r="C31" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D31" t="s">
         <v>293</v>
@@ -2401,7 +2401,7 @@
         <v>263</v>
       </c>
       <c r="C34" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D34" t="s">
         <v>296</v>
@@ -2443,7 +2443,7 @@
         <v>259</v>
       </c>
       <c r="C37" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D37" t="s">
         <v>299</v>
@@ -2457,7 +2457,7 @@
         <v>262</v>
       </c>
       <c r="C38" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D38" t="s">
         <v>300</v>
@@ -2471,7 +2471,7 @@
         <v>263</v>
       </c>
       <c r="C39" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="D39" t="s">
         <v>301</v>
@@ -2499,7 +2499,7 @@
         <v>261</v>
       </c>
       <c r="C41" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D41" t="s">
         <v>303</v>
@@ -2555,7 +2555,7 @@
         <v>261</v>
       </c>
       <c r="C45" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D45" t="s">
         <v>307</v>
@@ -2569,7 +2569,7 @@
         <v>259</v>
       </c>
       <c r="C46" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D46" t="s">
         <v>308</v>
@@ -2583,7 +2583,7 @@
         <v>262</v>
       </c>
       <c r="C47" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D47" t="s">
         <v>309</v>
@@ -2597,7 +2597,7 @@
         <v>262</v>
       </c>
       <c r="C48" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D48" t="s">
         <v>310</v>
@@ -2611,7 +2611,7 @@
         <v>262</v>
       </c>
       <c r="C49" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D49" t="s">
         <v>311</v>
@@ -2639,7 +2639,7 @@
         <v>261</v>
       </c>
       <c r="C51" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D51" t="s">
         <v>313</v>
@@ -2653,7 +2653,7 @@
         <v>261</v>
       </c>
       <c r="C52" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D52" t="s">
         <v>314</v>
@@ -2751,7 +2751,7 @@
         <v>261</v>
       </c>
       <c r="C59" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D59" t="s">
         <v>321</v>
@@ -2849,7 +2849,7 @@
         <v>263</v>
       </c>
       <c r="C66" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="D66" t="s">
         <v>328</v>
@@ -2877,7 +2877,7 @@
         <v>262</v>
       </c>
       <c r="C68" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D68" t="s">
         <v>330</v>
@@ -2905,7 +2905,7 @@
         <v>259</v>
       </c>
       <c r="C70" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D70" t="s">
         <v>332</v>
@@ -2933,7 +2933,7 @@
         <v>261</v>
       </c>
       <c r="C72" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="D72" t="s">
         <v>334</v>
@@ -2947,7 +2947,7 @@
         <v>263</v>
       </c>
       <c r="C73" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="D73" t="s">
         <v>335</v>
@@ -2961,7 +2961,7 @@
         <v>263</v>
       </c>
       <c r="C74" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="D74" t="s">
         <v>336</v>
@@ -2989,7 +2989,7 @@
         <v>262</v>
       </c>
       <c r="C76" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="D76" t="s">
         <v>338</v>
@@ -3003,7 +3003,7 @@
         <v>260</v>
       </c>
       <c r="C77" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D77" t="s">
         <v>339</v>
@@ -3017,7 +3017,7 @@
         <v>260</v>
       </c>
       <c r="C78" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D78" t="s">
         <v>340</v>
@@ -3045,7 +3045,7 @@
         <v>260</v>
       </c>
       <c r="C80" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D80" t="s">
         <v>342</v>
@@ -3059,7 +3059,7 @@
         <v>260</v>
       </c>
       <c r="C81" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D81" t="s">
         <v>343</v>
@@ -3073,7 +3073,7 @@
         <v>260</v>
       </c>
       <c r="C82" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D82" t="s">
         <v>344</v>
@@ -3087,7 +3087,7 @@
         <v>263</v>
       </c>
       <c r="C83" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="D83" t="s">
         <v>345</v>
@@ -3101,7 +3101,7 @@
         <v>261</v>
       </c>
       <c r="C84" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="D84" t="s">
         <v>346</v>
@@ -3115,7 +3115,7 @@
         <v>263</v>
       </c>
       <c r="C85" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="D85" t="s">
         <v>347</v>
@@ -3129,7 +3129,7 @@
         <v>263</v>
       </c>
       <c r="C86" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="D86" t="s">
         <v>348</v>
@@ -3143,7 +3143,7 @@
         <v>263</v>
       </c>
       <c r="C87" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="D87" t="s">
         <v>349</v>
@@ -3157,7 +3157,7 @@
         <v>262</v>
       </c>
       <c r="C88" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="D88" t="s">
         <v>350</v>
@@ -3409,7 +3409,7 @@
         <v>261</v>
       </c>
       <c r="C106" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D106" t="s">
         <v>368</v>
@@ -3437,7 +3437,7 @@
         <v>261</v>
       </c>
       <c r="C108" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D108" t="s">
         <v>370</v>
@@ -3451,7 +3451,7 @@
         <v>262</v>
       </c>
       <c r="C109" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D109" t="s">
         <v>371</v>
@@ -3465,7 +3465,7 @@
         <v>262</v>
       </c>
       <c r="C110" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D110" t="s">
         <v>372</v>
@@ -3479,7 +3479,7 @@
         <v>262</v>
       </c>
       <c r="C111" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D111" t="s">
         <v>373</v>
@@ -3493,7 +3493,7 @@
         <v>262</v>
       </c>
       <c r="C112" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D112" t="s">
         <v>374</v>
@@ -3507,7 +3507,7 @@
         <v>262</v>
       </c>
       <c r="C113" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D113" t="s">
         <v>375</v>
@@ -3563,7 +3563,7 @@
         <v>261</v>
       </c>
       <c r="C117" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D117" t="s">
         <v>379</v>
@@ -3605,7 +3605,7 @@
         <v>262</v>
       </c>
       <c r="C120" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D120" t="s">
         <v>382</v>
@@ -3619,7 +3619,7 @@
         <v>262</v>
       </c>
       <c r="C121" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D121" t="s">
         <v>383</v>
@@ -3633,7 +3633,7 @@
         <v>262</v>
       </c>
       <c r="C122" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D122" t="s">
         <v>384</v>
@@ -3647,7 +3647,7 @@
         <v>262</v>
       </c>
       <c r="C123" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D123" t="s">
         <v>385</v>
@@ -3661,7 +3661,7 @@
         <v>263</v>
       </c>
       <c r="C124" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="D124" t="s">
         <v>386</v>
@@ -3675,7 +3675,7 @@
         <v>262</v>
       </c>
       <c r="C125" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D125" t="s">
         <v>387</v>
@@ -3703,7 +3703,7 @@
         <v>259</v>
       </c>
       <c r="C127" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D127" t="s">
         <v>389</v>
@@ -3829,7 +3829,7 @@
         <v>263</v>
       </c>
       <c r="C136" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="D136" t="s">
         <v>398</v>
@@ -3843,7 +3843,7 @@
         <v>261</v>
       </c>
       <c r="C137" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="D137" t="s">
         <v>399</v>
@@ -3857,7 +3857,7 @@
         <v>261</v>
       </c>
       <c r="C138" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D138" t="s">
         <v>400</v>
@@ -3871,7 +3871,7 @@
         <v>261</v>
       </c>
       <c r="C139" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D139" t="s">
         <v>401</v>
@@ -3913,7 +3913,7 @@
         <v>261</v>
       </c>
       <c r="C142" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D142" t="s">
         <v>404</v>
@@ -3927,7 +3927,7 @@
         <v>259</v>
       </c>
       <c r="C143" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D143" t="s">
         <v>405</v>
@@ -3941,7 +3941,7 @@
         <v>260</v>
       </c>
       <c r="C144" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D144" t="s">
         <v>406</v>
@@ -3969,7 +3969,7 @@
         <v>260</v>
       </c>
       <c r="C146" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D146" t="s">
         <v>408</v>
@@ -3983,7 +3983,7 @@
         <v>260</v>
       </c>
       <c r="C147" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D147" t="s">
         <v>409</v>
@@ -3997,7 +3997,7 @@
         <v>263</v>
       </c>
       <c r="C148" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="D148" t="s">
         <v>410</v>
@@ -4025,7 +4025,7 @@
         <v>262</v>
       </c>
       <c r="C150" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D150" t="s">
         <v>412</v>
@@ -4053,7 +4053,7 @@
         <v>262</v>
       </c>
       <c r="C152" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D152" t="s">
         <v>414</v>
@@ -4081,7 +4081,7 @@
         <v>259</v>
       </c>
       <c r="C154" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D154" t="s">
         <v>416</v>
@@ -4137,7 +4137,7 @@
         <v>259</v>
       </c>
       <c r="C158" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D158" t="s">
         <v>420</v>
@@ -4193,7 +4193,7 @@
         <v>262</v>
       </c>
       <c r="C162" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D162" t="s">
         <v>424</v>
@@ -4361,7 +4361,7 @@
         <v>259</v>
       </c>
       <c r="C174" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D174" t="s">
         <v>436</v>
@@ -4515,7 +4515,7 @@
         <v>261</v>
       </c>
       <c r="C185" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D185" t="s">
         <v>447</v>
@@ -4543,7 +4543,7 @@
         <v>261</v>
       </c>
       <c r="C187" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D187" t="s">
         <v>449</v>
@@ -4571,7 +4571,7 @@
         <v>261</v>
       </c>
       <c r="C189" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D189" t="s">
         <v>451</v>
@@ -4585,7 +4585,7 @@
         <v>259</v>
       </c>
       <c r="C190" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D190" t="s">
         <v>452</v>
@@ -4599,7 +4599,7 @@
         <v>259</v>
       </c>
       <c r="C191" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D191" t="s">
         <v>453</v>
@@ -4613,7 +4613,7 @@
         <v>259</v>
       </c>
       <c r="C192" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D192" t="s">
         <v>454</v>
@@ -4641,7 +4641,7 @@
         <v>261</v>
       </c>
       <c r="C194" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D194" t="s">
         <v>456</v>
@@ -4683,7 +4683,7 @@
         <v>259</v>
       </c>
       <c r="C197" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D197" t="s">
         <v>459</v>
@@ -4711,7 +4711,7 @@
         <v>262</v>
       </c>
       <c r="C199" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D199" t="s">
         <v>461</v>
@@ -4823,7 +4823,7 @@
         <v>259</v>
       </c>
       <c r="C207" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D207" t="s">
         <v>469</v>
@@ -4851,7 +4851,7 @@
         <v>261</v>
       </c>
       <c r="C209" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D209" t="s">
         <v>471</v>
@@ -5033,7 +5033,7 @@
         <v>259</v>
       </c>
       <c r="C222" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D222" t="s">
         <v>484</v>
@@ -5089,7 +5089,7 @@
         <v>261</v>
       </c>
       <c r="C226" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D226" t="s">
         <v>488</v>
@@ -5117,7 +5117,7 @@
         <v>261</v>
       </c>
       <c r="C228" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D228" t="s">
         <v>490</v>
@@ -5145,7 +5145,7 @@
         <v>261</v>
       </c>
       <c r="C230" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D230" t="s">
         <v>492</v>
@@ -5159,7 +5159,7 @@
         <v>261</v>
       </c>
       <c r="C231" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D231" t="s">
         <v>493</v>
@@ -5187,7 +5187,7 @@
         <v>259</v>
       </c>
       <c r="C233" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D233" t="s">
         <v>495</v>
@@ -5327,7 +5327,7 @@
         <v>261</v>
       </c>
       <c r="C243" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D243" t="s">
         <v>505</v>
@@ -5369,7 +5369,7 @@
         <v>261</v>
       </c>
       <c r="C246" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D246" t="s">
         <v>508</v>
@@ -5397,7 +5397,7 @@
         <v>261</v>
       </c>
       <c r="C248" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D248" t="s">
         <v>510</v>
@@ -5411,7 +5411,7 @@
         <v>261</v>
       </c>
       <c r="C249" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D249" t="s">
         <v>511</v>
@@ -5439,7 +5439,7 @@
         <v>259</v>
       </c>
       <c r="C251" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D251" t="s">
         <v>513</v>
@@ -5453,7 +5453,7 @@
         <v>260</v>
       </c>
       <c r="C252" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D252" t="s">
         <v>514</v>
@@ -5467,7 +5467,7 @@
         <v>260</v>
       </c>
       <c r="C253" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D253" t="s">
         <v>515</v>
@@ -5481,7 +5481,7 @@
         <v>260</v>
       </c>
       <c r="C254" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D254" t="s">
         <v>516</v>
@@ -5495,7 +5495,7 @@
         <v>260</v>
       </c>
       <c r="C255" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D255" t="s">
         <v>517</v>
